--- a/source/relatorios/2025/2-fev.xlsx
+++ b/source/relatorios/2025/2-fev.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t xml:space="preserve">Projeto</t>
   </si>
@@ -59,9 +59,6 @@
   </si>
   <si>
     <t xml:space="preserve">CP</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t xml:space="preserve">CPBMF</t>
@@ -262,8 +259,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G1048576"/>
-  <sheetFormatPr defaultColWidth="12.8125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G36"/>
+  <sheetFormatPr defaultColWidth="12.796875" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -392,9 +389,7 @@
         <v>210</v>
       </c>
       <c r="D7" s="2"/>
-      <c r="E7" s="1" t="s">
-        <v>13</v>
-      </c>
+      <c r="E7" s="1"/>
       <c r="F7" s="2"/>
       <c r="G7" s="1" t="n">
         <v>2</v>
@@ -402,7 +397,7 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>5</v>
@@ -425,7 +420,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>5</v>
@@ -442,7 +437,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>5</v>
@@ -459,7 +454,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>5</v>
@@ -476,7 +471,7 @@
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>5</v>
@@ -493,7 +488,7 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>5</v>
@@ -516,7 +511,7 @@
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>5</v>
@@ -537,7 +532,7 @@
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>5</v>
@@ -556,7 +551,7 @@
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>5</v>
@@ -573,7 +568,7 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>5</v>
@@ -592,7 +587,7 @@
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>5</v>
@@ -613,7 +608,7 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>5</v>
@@ -634,7 +629,7 @@
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>5</v>
@@ -657,7 +652,7 @@
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>5</v>
@@ -674,7 +669,7 @@
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>5</v>
@@ -691,7 +686,7 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>5</v>
@@ -708,7 +703,7 @@
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>5</v>
@@ -725,7 +720,7 @@
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>5</v>
@@ -744,7 +739,7 @@
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>5</v>
@@ -767,7 +762,7 @@
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>5</v>
@@ -786,7 +781,7 @@
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>5</v>
@@ -807,7 +802,7 @@
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>5</v>
@@ -824,7 +819,7 @@
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>5</v>
@@ -841,7 +836,7 @@
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>5</v>
@@ -858,7 +853,7 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>5</v>
@@ -875,7 +870,7 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>5</v>
@@ -894,7 +889,7 @@
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" s="1" t="n">
         <v>5</v>
@@ -911,7 +906,7 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" s="3" t="n">
         <v>216</v>
@@ -920,7 +915,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="G36" s="1"/>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
